--- a/data/trans_orig/IP31KM15_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM15_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78309</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67538</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89714</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>63192</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54429</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71183</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>65391</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67949</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98150</t>
+          <t>75825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>145090</t>
+          <t>143701</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129578</t>
+          <t>129448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164138</t>
+          <t>157894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44587</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33182</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55358</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51059</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43068</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59822</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54918</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38665</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68866</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>97793</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86928</t>
+          <t>83600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121488</t>
+          <t>112046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121554</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>106907</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>134859</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>105217</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>91808</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117051</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>56,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>62,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127427</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111920</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142317</t>
+          <t>117175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>232645</t>
+          <t>227093</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>209853</t>
+          <t>208471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252551</t>
+          <t>245249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96382</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>124334</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>47,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>80897</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69063</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94306</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>120093</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105203</t>
+          <t>63418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135600</t>
+          <t>86932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>200989</t>
+          <t>184740</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181083</t>
+          <t>166584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>223781</t>
+          <t>203362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76110</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63728</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>89595</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>82546</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48147</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101599</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86073</t>
+          <t>80302</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72334</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99262</t>
+          <t>91300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>156412</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>139756</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>174337</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>48,64%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>43,46%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>54,22%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>168619</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>130069</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>191854</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90412</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76927</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102794</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>105703</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86650</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140102</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97016</t>
+          <t>74736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83827</t>
+          <t>63738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110755</t>
+          <t>85278</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>55,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>165148</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>147223</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>181804</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>51,36%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>45,78%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>202720</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>179485</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>241270</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>104134</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93531</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113753</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>110904</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100557</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>120604</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>109214</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>98221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122360</t>
+          <t>118445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>221100</t>
+          <t>213347</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204955</t>
+          <t>199187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>228078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62031</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52412</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72634</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>53615</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43915</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>54765</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54949</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77901</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>120728</t>
+          <t>116797</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106303</t>
+          <t>102066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>130957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>380108</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>356711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>407480</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>361860</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>311478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>388284</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378260</t>
+          <t>337793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431631</t>
+          <t>380812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>715739</t>
+          <t>707394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>806798</t>
+          <t>776670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>306716</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>279344</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>330113</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>380</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>291274</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>264850</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341656</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>339140</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313102</t>
+          <t>237396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366473</t>
+          <t>280415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>564478</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>591069</t>
+          <t>528361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682128</t>
+          <t>597637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
